--- a/import_template/合同导入模板样例.xlsx
+++ b/import_template/合同导入模板样例.xlsx
@@ -424,26 +424,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -498,30 +480,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>所属框架编号</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>是否框架</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>标签(逗号分隔)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>质保金额</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>质保比例%</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>质保生效日期</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>质保期限(月)</t>
         </is>
@@ -558,9 +550,6 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>132000</v>
-      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -574,24 +563,29 @@
           <t>内部审批中</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>采购,项目A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>6600</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>5</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>12</v>
       </c>
     </row>
@@ -626,9 +620,6 @@
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>6000</v>
-      </c>
       <c r="H3" t="n">
         <v>6000</v>
       </c>
@@ -642,24 +633,29 @@
           <t>到货</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>销售</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>300</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>5</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -676,24 +672,6 @@
   </sheetPr>
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -852,11 +830,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -868,49 +843,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. 两个工作表都要填：『合同(主档)』每行一个合同；『行项明细』每行一个明细，同一合同的明细序号连续。</t>
+          <t>1. 必填：合同编号（唯一，不可与库内重复）、合同名称；类型/甲方/乙方/签订日期 建议都填。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2. 金额/已付/数量/单价/比例 只填数字；签订日期/质保生效日期填 YYYY-MM-DD。</t>
+          <t>2. 两个工作表都要填：『合同(主档)』每行一个合同；『行项明细』按合同编号挂行（同一合同序号连续）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3. 标签列多个标签用英文逗号分隔（如：采购,项目A），系统里不存在的标签会自动创建。</t>
+          <t>3. 金额/数量/单价/比例只填数字；日期填 YYYY-MM-DD。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4. 金额留空 = 由行项合计自动计算；若某合同没有行项（如框架/预估），金额必须手填。</t>
+          <t>4. 金额留空 = 由行项合计自动计算（推荐）；若合同没有行项，金额必须手填。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. 同一合同编号只出现一次；重复、必填缺失、日期或数字格式错误的行会整条跳过并写入错误报告。</t>
+          <t>5. 标签列多个标签用英文逗号分隔；系统不存在的标签会自动创建。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6. 状态可选：内部审批中/集团审批中/已签订/付款中/发货/到货/已终止（留空默认为内部审批中）。</t>
+          <t>6. 状态可选：内部审批中/集团审批中/已签订/付款中/发货/到货/已终止（留空默认内部审批中）。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7. 示例行可整行删除后再填写，导入前建议用真实数据先试 3~5 条。</t>
+          <t>7. 是否框架：是/否；所属框架编号填已存在框架合同的编号（子合同可挂到框架下）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8. 同一合同编号只出现一次：文件内重复、与库内重复、必填缺失、格式错误的行会整条跳过并写入错误报告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9. 示例行请整行删除后再填写；上线前先用真实数据试 3~5 条。</t>
         </is>
       </c>
     </row>

--- a/import_template/合同导入模板样例.xlsx
+++ b/import_template/合同导入模板样例.xlsx
@@ -424,238 +424,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>合同编号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>合同名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>主体码</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>甲方</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>乙方</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>签订日期</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>已付金额</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>经办人</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>所属框架编号</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>是否框架</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>标签(逗号分隔)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>质保金额</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>质保比例%</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>质保生效日期</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>质保期限(月)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CG-2026-101</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>示例：新购设备合同</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>采购</t>
+          <t>示例：新购设备合同（自动编号）</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>采购/支出</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>本公司（甲方示例）</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>XX 供应商</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>内部审批中</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>采购,项目A</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>6600</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>XS-2026-201</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>示例：产品销售</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>示例：产品销售（自动编号）</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ZC</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>客户 M 公司</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>本公司（乙方示例）</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>到货</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>销售</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>客户 M 公司</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>本公司（乙方示例）</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>300</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>到货</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>销售</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>300</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>12</v>
       </c>
     </row>
@@ -676,7 +692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>合同编号(对应主档)</t>
+          <t>主档序号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -716,10 +732,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CG-2026-101</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -752,10 +766,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CG-2026-101</t>
-        </is>
+      <c r="A3" t="n">
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -784,10 +796,8 @@
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>XS-2026-201</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -830,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,63 +853,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. 必填：合同编号（唯一，不可与库内重复）、合同名称；类型/甲方/乙方/签订日期 建议都填。</t>
+          <t>1. 工作表『合同(主档)』每行一个合同：『序号』填 1,2,3…（行项明细用它在明细表引用该合同）；示例行删除后填写。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2. 两个工作表都要填：『合同(主档)』每行一个合同；『行项明细』按合同编号挂行（同一合同序号连续）。</t>
+          <t>2. 『合同编号』：留空 = 系统自动生成（类型码+主体码+年份+月份+6位序号，年度递增，如 PURZC202609000001）；也可手填（需唯一、不重复）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3. 金额/数量/单价/比例只填数字；日期填 YYYY-MM-DD。</t>
+          <t>3. 『类型』必填：填名称（销售/收入、采购/支出、合作/战略协议、劳动/人事、金融/投融资、保密协议）或代码（SAL/PUR/COO/LAB/FIN/NDA）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4. 金额留空 = 由行项合计自动计算（推荐）；若合同没有行项，金额必须手填。</t>
+          <t>4. 『主体码』：我方公司，ZC=智澈公司 / YX=云羲公司（可空，默认第一个可用主体）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. 标签列多个标签用英文逗号分隔；系统不存在的标签会自动创建。</t>
+          <t>5. 『行项明细』工作表：『主档序号』填其归属合同在“合同(主档)”里的序号；同一合同的行项序号连续；无行项的合同，金额必须手填。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6. 状态可选：内部审批中/集团审批中/已签订/付款中/发货/到货/已终止（留空默认内部审批中）。</t>
+          <t>6. 金额留空=按行项合计自动；金额/数量/单价/比例只填数字；日期填 YYYY-MM-DD。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7. 是否框架：是/否；所属框架编号填已存在框架合同的编号（子合同可挂到框架下）。</t>
+          <t>7. 标签列多个用英文逗号分隔，不存在会自动创建；类型会自动带【类型名】标签。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8. 同一合同编号只出现一次：文件内重复、与库内重复、必填缺失、格式错误的行会整条跳过并写入错误报告。</t>
+          <t>8. 状态可选：内部审批中/集团审批中/已签订/付款中/发货/到货/已终止（留空默认内部审批中）。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9. 示例行请整行删除后再填写；上线前先用真实数据试 3~5 条。</t>
+          <t>9. 是否框架填是/否；所属框架编号填已存在框架合同编号（子合同自动挂到其下）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10. 同一合同编号只出现一次：文件内重复、与库内重复、必填缺失、格式错误的行会整条跳过并写入错误报告。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11. 上线前请先用真实数据试 3~5 条。</t>
         </is>
       </c>
     </row>
